--- a/data/trans_orig/KIDMED_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30484</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>26922</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>57405</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>50289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63097</t>
+          <t>64512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32351</t>
+          <t>31456</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39103</t>
+          <t>38909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103280</t>
+          <t>102588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122416</t>
+          <t>122141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,82 +1201,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>190</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>123640</t>
+          <t>125906</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112102</t>
+          <t>115655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133719</t>
+          <t>136095</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>372</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>236559</t>
+          <t>238825</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>222778</t>
+          <t>225414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249483</t>
+          <t>254027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>37101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55662</t>
+          <t>56343</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,82 +1314,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>50761</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64437</t>
+          <t>61033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>153</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>99019</t>
+          <t>96753</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>86744</t>
+          <t>81863</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113934</t>
+          <t>110786</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1632,107 +1632,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>106362</t>
+          <t>108366</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94916</t>
+          <t>95526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117359</t>
+          <t>119783</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>141029</t>
+          <t>142000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127784</t>
+          <t>128230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153694</t>
+          <t>155117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>316</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>247392</t>
+          <t>250366</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>229572</t>
+          <t>231676</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>264611</t>
+          <t>266890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -1745,107 +1745,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51209</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74829</t>
+          <t>72968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>66976</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55409</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81526</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>150</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>129869</t>
+          <t>126894</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113914</t>
+          <t>110344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148598</t>
+          <t>145209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2088,107 +2088,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>197</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>142245</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99428</t>
+          <t>96827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163417</t>
+          <t>162781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>211</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>170126</t>
+          <t>171288</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146101</t>
+          <t>145940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187822</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>408</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>311839</t>
+          <t>313534</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263091</t>
+          <t>262973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342653</t>
+          <t>343805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>121573</t>
+          <t>121041</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99553</t>
+          <t>99402</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167620</t>
+          <t>169922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>36,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>61,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>120509</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>101004</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145023</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>33,12%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>241550</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>210251</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>295705</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>36,3%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,12%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>121672</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>102982</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>148138</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,89%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>48,57%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>243244</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>210797</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>296326</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>41,99%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>36,39%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35277</t>
+          <t>34777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -2544,107 +2544,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>391062</t>
+          <t>394014</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>338588</t>
+          <t>342979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>418124</t>
+          <t>421661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>461237</t>
+          <t>466116</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>428847</t>
+          <t>435981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>487817</t>
+          <t>495052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>852300</t>
+          <t>860130</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>787861</t>
+          <t>796725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>891020</t>
+          <t>899449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>245518</t>
+          <t>242566</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>219739</t>
+          <t>214177</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>302666</t>
+          <t>294628</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>258966</t>
+          <t>254087</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>232911</t>
+          <t>224987</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>290726</t>
+          <t>285754</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>603</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>504483</t>
+          <t>496653</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>466861</t>
+          <t>457445</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>573183</t>
+          <t>565634</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>24904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35530</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>54260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KIDMED_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
+          <t>Menores según tipo de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23188</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18956</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26963</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>30484</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25058</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50289</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>57695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38909</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2065</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6031</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108827</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98736</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118566</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>112918</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>102588</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>122141</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>125906</t>
+          <t>102538</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115655</t>
+          <t>92953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136095</t>
+          <t>110547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>238825</t>
+          <t>211364</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225414</t>
+          <t>198361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254027</t>
+          <t>223585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43516</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>34444</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>53723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>45991</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37101</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>56343</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>23,29%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50761</t>
+          <t>42656</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41112</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61033</t>
+          <t>52014</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>96753</t>
+          <t>86172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81863</t>
+          <t>74317</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110786</t>
+          <t>99009</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4699</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9967</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5292</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10854</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>134851</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>121246</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>145830</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>72,87%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>108366</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>95526</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>119783</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>62,61%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>69,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>142000</t>
+          <t>113870</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>128230</t>
+          <t>102296</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155117</t>
+          <t>123860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>250366</t>
+          <t>248721</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>231676</t>
+          <t>232290</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>266890</t>
+          <t>264429</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>61788</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48834</t>
+          <t>51588</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72968</t>
+          <t>75073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66976</t>
+          <t>55749</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>45485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>67117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>126894</t>
+          <t>117537</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110344</t>
+          <t>102255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145209</t>
+          <t>133756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8422</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4788</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10723</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>172157</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>152772</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>189857</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>142245</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>96827</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>162781</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>51,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>171288</t>
+          <t>148678</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>145940</t>
+          <t>134224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190414</t>
+          <t>162881</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>313534</t>
+          <t>320835</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>262973</t>
+          <t>295345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343805</t>
+          <t>345746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>107871</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>91158</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127882</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>121041</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>99402</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>169922</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>44,13%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>120509</t>
+          <t>95125</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101004</t>
+          <t>81585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145023</t>
+          <t>109717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>241550</t>
+          <t>202995</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210251</t>
+          <t>179216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295705</t>
+          <t>226913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -2314,107 +2314,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12193</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20847</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>10981</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6179</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18218</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>23728</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>15951</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>35203</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>24182</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>16213</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>34777</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>585</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>394014</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>342979</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>421661</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>374528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>412911</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>796725</t>
+          <t>798965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>899449</t>
+          <t>863679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>225430</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>201867</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>254502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>37,05%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>242566</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>214177</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>294628</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>254087</t>
+          <t>207320</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>224987</t>
+          <t>189683</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>285754</t>
+          <t>227608</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>496653</t>
+          <t>432750</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>457445</t>
+          <t>403133</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>565634</t>
+          <t>466004</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>24904</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
